--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,7 +513,7 @@
     <t>Document Références d'objets d'un examen d'imagerie selon profil IHE RAD XDS-I</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A09-DICOMuidRegistry/FHIR/TRE-A09-DICOMuidRegistry</t>
+    <t>http://dicom.nema.org/resources/ontology/DCMUID</t>
   </si>
   <si>
     <t>urn:oid:1.3.6.1.4.1.19376.1.2.1.1.1</t>

--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,7 +513,7 @@
     <t>Document Références d'objets d'un examen d'imagerie selon profil IHE RAD XDS-I</t>
   </si>
   <si>
-    <t>http://dicom.nema.org/resources/ontology/DCMUID</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A09-DICOMuidRegistry/FHIR/TRE-A09-DICOMuidRegistry</t>
   </si>
   <si>
     <t>urn:oid:1.3.6.1.4.1.19376.1.2.1.1.1</t>
